--- a/03-Excel/A376/新书订购表.xlsx
+++ b/03-Excel/A376/新书订购表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyCode\A376\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shuaishi/code/HiPython/03-Excel/A376/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA63363A-F087-42A7-8B46-E9D55E33A1B1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D14568E-3333-0F4D-AED1-D62CB6E2A9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="3570" windowWidth="8235" windowHeight="7350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="3580" windowWidth="10000" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新书订购表" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,13 +101,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -411,14 +408,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="30.875" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -426,7 +423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -434,7 +431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -442,17 +439,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="163.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
